--- a/Client/Configs/GameConfig/Datas/enemy_level.xlsx
+++ b/Client/Configs/GameConfig/Datas/enemy_level.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,94 +513,94 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##</t>
+          <t>##group</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Enemy level row id.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Enemy id.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Enemy level.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hp multiplier.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Attack multiplier.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Defense multiplier.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Exp multiplier.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Gold multiplier.</t>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>##group</t>
+          <t>##</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Enemy level row id.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Enemy id.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Enemy level.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Hp multiplier.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Attack multiplier.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Defense multiplier.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Exp multiplier.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Gold multiplier.</t>
         </is>
       </c>
     </row>
@@ -632,80 +632,756 @@
     </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>100201</v>
+        <v>100102</v>
       </c>
       <c r="C6" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>100202</v>
+        <v>100103</v>
       </c>
       <c r="C7" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="F7" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="H7" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="I7" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
+        <v>100104</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>100105</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>100106</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>100107</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>100108</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>100110</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>100201</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>100202</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>100203</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>100204</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>100205</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>100206</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>100207</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>100208</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D22" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>100209</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>100210</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>900101</v>
+      </c>
+      <c r="C25" t="n">
+        <v>9001</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>900102</v>
+      </c>
+      <c r="C26" t="n">
+        <v>9001</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.342</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.197</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
         <v>900103</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C27" t="n">
         <v>9001</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D27" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E27" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.344</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>900104</v>
+      </c>
+      <c r="C28" t="n">
+        <v>9001</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.491</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>900105</v>
+      </c>
+      <c r="C29" t="n">
+        <v>9001</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.068</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.638</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>900106</v>
+      </c>
+      <c r="C30" t="n">
+        <v>9001</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.785</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>900107</v>
+      </c>
+      <c r="C31" t="n">
+        <v>9001</v>
+      </c>
+      <c r="D31" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.552</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.932</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>900108</v>
+      </c>
+      <c r="C32" t="n">
+        <v>9001</v>
+      </c>
+      <c r="D32" t="n">
+        <v>8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.794</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.079</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>900109</v>
+      </c>
+      <c r="C33" t="n">
+        <v>9001</v>
+      </c>
+      <c r="D33" t="n">
+        <v>9</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.036</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.226</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>900110</v>
+      </c>
+      <c r="C34" t="n">
+        <v>9001</v>
+      </c>
+      <c r="D34" t="n">
         <v>10</v>
       </c>
-      <c r="F8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5</v>
+      <c r="E34" t="n">
+        <v>3.278</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.373</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.62</v>
       </c>
     </row>
   </sheetData>
